--- a/Packing_Declaration_MONAT_AUS.xlsx
+++ b/Packing_Declaration_MONAT_AUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leudineglobal-my.sharepoint.com/personal/kalvarez_monatglobal_com/Documents/LOGISTIC PAPERWORK GENERATOR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B621771-87BA-463F-88E3-7C68033EADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7B621771-87BA-463F-88E3-7C68033EADD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C51A3F2E-54C1-43FD-B5B9-8DC6049DDC43}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -572,9 +572,6 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -590,49 +587,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -649,13 +603,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -664,6 +620,61 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -676,26 +687,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,155 +1091,155 @@
     <row r="5" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="28"/>
     </row>
     <row r="11" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="61" t="s">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="62"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="18"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="14" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="18"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="17"/>
     </row>
     <row r="15" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="23"/>
     </row>
     <row r="17" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="54"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59"/>
     </row>
     <row r="18" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="52" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="56"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="31"/>
     </row>
     <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -1250,60 +1251,60 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="32"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
     </row>
     <row r="22" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="51"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="35"/>
     </row>
     <row r="23" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="22"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="42"/>
     </row>
     <row r="24" spans="1:13" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="52" t="s">
         <v>16</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -1312,277 +1313,277 @@
       <c r="C24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="38"/>
+      <c r="E24" s="20"/>
       <c r="F24" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="G24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="38"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="45" t="s">
+      <c r="J24" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="46"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="31"/>
     </row>
     <row r="25" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="32"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="28"/>
     </row>
     <row r="27" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="22"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="42"/>
     </row>
     <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
       <c r="K28" s="4"/>
       <c r="L28" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="M28" s="57"/>
+      <c r="M28" s="47"/>
     </row>
     <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="22"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="42"/>
     </row>
     <row r="30" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
-      <c r="B30" s="21" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
       <c r="K30" s="4"/>
       <c r="L30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M30" s="57"/>
+      <c r="M30" s="47"/>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
-      <c r="B31" s="55" t="s">
+      <c r="A31" s="32"/>
+      <c r="B31" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
       <c r="K31" s="8"/>
       <c r="L31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M31" s="59"/>
+      <c r="M31" s="51"/>
     </row>
     <row r="32" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:13" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="32"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="28"/>
     </row>
     <row r="34" spans="1:13" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="32"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="28"/>
     </row>
     <row r="35" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="14" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
     </row>
     <row r="37" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
     </row>
     <row r="38" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="12" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
     </row>
     <row r="39" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
     </row>
     <row r="41" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="47"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
+      <c r="A41" s="63"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
     </row>
     <row r="42" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -1600,27 +1601,26 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="A17:M17"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="I19:M19"/>
-    <mergeCell ref="M28"/>
-    <mergeCell ref="G36:M36"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A43:M43"/>
     <mergeCell ref="B27:M27"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A23"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="B23:M23"/>
-    <mergeCell ref="A18"/>
-    <mergeCell ref="E40:M40"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A34:M34"/>
     <mergeCell ref="A28"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="B29:M29"/>
     <mergeCell ref="G37:M37"/>
     <mergeCell ref="A33:M33"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="I19:M19"/>
+    <mergeCell ref="M28"/>
+    <mergeCell ref="G36:M36"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="A40:D40"/>
@@ -1633,9 +1633,10 @@
     <mergeCell ref="A26:M26"/>
     <mergeCell ref="G38:M38"/>
     <mergeCell ref="J24:M24"/>
-    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A31"/>
     <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A18"/>
+    <mergeCell ref="E40:M40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="72" orientation="portrait" r:id="rId1"/>
